--- a/Result/checksun_type/中藥材、西藥原料藥.xlsx
+++ b/Result/checksun_type/中藥材、西藥原料藥.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI189"/>
+  <dimension ref="A1:CI199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76734,42 +76734,42 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>54.837</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -76779,37 +76779,37 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -76819,12 +76819,12 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
@@ -76834,32 +76834,32 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr"/>
@@ -76875,121 +76875,121 @@
       </c>
       <c r="AF178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.05</t>
         </is>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-105.63</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1371045.0</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2624601.4</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1944877.5</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3069952.5</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679723</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-225586.3440859158</t>
         </is>
       </c>
       <c r="BC178" t="n">
-        <v>0</v>
+        <v>-202165.01</v>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
@@ -76998,17 +76998,17 @@
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="BH178" t="inlineStr">
@@ -77053,7 +77053,7 @@
       </c>
       <c r="BP178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ178" t="inlineStr">
@@ -77063,7 +77063,7 @@
       </c>
       <c r="BR178" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS178" t="inlineStr">
@@ -77118,22 +77118,22 @@
       </c>
       <c r="CC178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CD178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CE178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG178" t="inlineStr">
@@ -77160,17 +77160,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>3690.931</t>
+          <t>162.03</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -77180,7 +77180,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -77190,17 +77190,17 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-2.49</t>
-        </is>
-      </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -77210,37 +77210,37 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -77250,12 +77250,12 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
@@ -77265,27 +77265,27 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
@@ -77296,131 +77296,131 @@
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG179" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>-110.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>69701539.0</t>
+          <t>4102108.0</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>66070275.6</t>
+          <t>2587874.4</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>46567948.0</t>
+          <t>1991636.2</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>139781443.8</t>
+          <t>3064720.06</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>19502327</t>
+          <t>596238</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>-9002419.174373947</t>
+          <t>-229844.7680710168</t>
         </is>
       </c>
       <c r="BC179" t="n">
-        <v>595819.37</v>
+        <v>-125527.48</v>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
@@ -77429,32 +77429,32 @@
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="BH179" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK179" t="inlineStr">
@@ -77464,47 +77464,47 @@
       </c>
       <c r="BL179" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM179" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN179" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO179" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP179" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ179" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR179" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS179" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT179" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU179" t="inlineStr">
@@ -77514,67 +77514,67 @@
       </c>
       <c r="BV179" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW179" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX179" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY179" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ179" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA179" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB179" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC179" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD179" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE179" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF179" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG179" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH179" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI179" t="inlineStr">
@@ -77591,17 +77591,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>6098.179</t>
+          <t>102.217</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -77611,7 +77611,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -77621,17 +77621,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -77641,37 +77641,37 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -77681,12 +77681,12 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
@@ -77696,27 +77696,27 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
@@ -77727,131 +77727,131 @@
       <c r="AC180" t="inlineStr"/>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG180" t="inlineStr">
         <is>
-          <t>98.25</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
+          <t>-2.43</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>25.52</t>
+        </is>
+      </c>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t>25.96</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>26.83</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>-20.50</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>18.56</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>31.82</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>-110.41</t>
+          <t>-105.41</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>118098812.0</t>
+          <t>2529530.0</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>57508673.0</t>
+          <t>1925522.0</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>42493200.7</t>
+          <t>1685808.2</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>139366944.98</t>
+          <t>3027110.7</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>15015472</t>
+          <t>239713</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>-10747553.45557433</t>
+          <t>-248811.5481608517</t>
         </is>
       </c>
       <c r="BC180" t="n">
-        <v>-248487.7</v>
+        <v>-304176.05</v>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
@@ -77860,32 +77860,32 @@
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="BH180" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK180" t="inlineStr">
@@ -77895,27 +77895,27 @@
       </c>
       <c r="BL180" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM180" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN180" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO180" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP180" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ180" t="inlineStr">
@@ -77925,17 +77925,17 @@
       </c>
       <c r="BR180" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS180" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT180" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU180" t="inlineStr">
@@ -77945,67 +77945,67 @@
       </c>
       <c r="BV180" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW180" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX180" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY180" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ180" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA180" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB180" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC180" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CD180" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE180" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF180" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG180" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH180" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI180" t="inlineStr">
@@ -78022,17 +78022,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>3990.59</t>
+          <t>88.096</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -78042,7 +78042,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -78072,37 +78072,37 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -78112,12 +78112,12 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -78127,27 +78127,27 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
@@ -78158,131 +78158,131 @@
       <c r="AC181" t="inlineStr"/>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG181" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>-28.02</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-105.14</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>76501817.0</t>
+          <t>2182171.0</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>37298069.0</t>
+          <t>1638268.0</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>33598142.9</t>
+          <t>1563699.4</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>138751251.62</t>
+          <t>3014053.16</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>3699926</t>
+          <t>74568</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>-12656474.50287244</t>
+          <t>-238745.2743788016</t>
         </is>
       </c>
       <c r="BC181" t="n">
-        <v>-6631188.2</v>
+        <v>-380034.38</v>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
@@ -78291,32 +78291,32 @@
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="BH181" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK181" t="inlineStr">
@@ -78326,27 +78326,27 @@
       </c>
       <c r="BL181" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM181" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN181" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO181" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP181" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ181" t="inlineStr">
@@ -78356,17 +78356,17 @@
       </c>
       <c r="BR181" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS181" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT181" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU181" t="inlineStr">
@@ -78376,67 +78376,67 @@
       </c>
       <c r="BV181" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW181" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX181" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY181" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ181" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA181" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB181" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC181" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CD181" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE181" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF181" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG181" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH181" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI181" t="inlineStr">
@@ -78453,17 +78453,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2201.558</t>
+          <t>118.827</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -78473,7 +78473,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -78483,17 +78483,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>-21.28</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -78503,37 +78503,37 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -78543,12 +78543,12 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -78558,27 +78558,27 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
@@ -78589,131 +78589,131 @@
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>58.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>26.08</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-34.89</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>-111.57</t>
+          <t>-104.78</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>41778653.0</t>
+          <t>2938153.0</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>26259471.0</t>
+          <t>1596404.4</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>33359343.4</t>
+          <t>1505715.3</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>138380212.08</t>
+          <t>3040907.36</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>-7099872</t>
+          <t>90689</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>-13751981.10415282</t>
+          <t>-213056.3469127035</t>
         </is>
       </c>
       <c r="BC182" t="n">
-        <v>-11055682.73</v>
+        <v>-437613.71</v>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
@@ -78722,32 +78722,32 @@
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>-12.72</t>
         </is>
       </c>
       <c r="BH182" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK182" t="inlineStr">
@@ -78757,47 +78757,47 @@
       </c>
       <c r="BL182" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM182" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN182" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO182" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP182" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ182" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR182" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BS182" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT182" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU182" t="inlineStr">
@@ -78807,67 +78807,67 @@
       </c>
       <c r="BV182" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW182" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX182" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY182" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ182" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA182" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB182" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC182" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CD182" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE182" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF182" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG182" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH182" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI182" t="inlineStr">
@@ -78884,17 +78884,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1303.305</t>
+          <t>47.487</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -78904,7 +78904,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -78914,17 +78914,17 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -78934,37 +78934,37 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
@@ -78974,12 +78974,12 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
@@ -78989,27 +78989,27 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
@@ -79020,131 +79020,131 @@
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG183" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>-47.05</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>-111.02</t>
+          <t>-104.36</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>24270557.0</t>
+          <t>1187410.0</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>24098185.0</t>
+          <t>1265153.6</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>33840923.3</t>
+          <t>1514701.9</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>140302562.8</t>
+          <t>3068333.78</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>-9742738</t>
+          <t>-249548</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>-14242217.17306861</t>
+          <t>-172227.7346880539</t>
         </is>
       </c>
       <c r="BC183" t="n">
-        <v>-13261204.38</v>
+        <v>-585238.92</v>
       </c>
       <c r="BD183" t="inlineStr">
         <is>
@@ -79153,32 +79153,32 @@
       </c>
       <c r="BE183" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG183" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="BH183" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI183" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ183" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK183" t="inlineStr">
@@ -79188,27 +79188,27 @@
       </c>
       <c r="BL183" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM183" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN183" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO183" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP183" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ183" t="inlineStr">
@@ -79218,17 +79218,17 @@
       </c>
       <c r="BR183" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS183" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT183" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU183" t="inlineStr">
@@ -79238,67 +79238,67 @@
       </c>
       <c r="BV183" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW183" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX183" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY183" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ183" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA183" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB183" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC183" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD183" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE183" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF183" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG183" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH183" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI183" t="inlineStr">
@@ -79315,17 +79315,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1467.935</t>
+          <t>31.607</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -79335,7 +79335,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -79345,17 +79345,17 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-2.49</t>
-        </is>
-      </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>-35.74</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -79365,37 +79365,37 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -79405,12 +79405,12 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
@@ -79420,27 +79420,27 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
@@ -79451,131 +79451,131 @@
       <c r="AC184" t="inlineStr"/>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>22.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>-69.03</t>
+          <t>-33.01</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>-109.72</t>
+          <t>-104.01</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>26893526.0</t>
+          <t>790346.0</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>27065620.4</t>
+          <t>1395398.0</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>42116606.3</t>
+          <t>1879101.2</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>141853229.66</t>
+          <t>3061448.2</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>-15050985</t>
+          <t>-483703</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>-14420583.13473333</t>
+          <t>-97134.79144795398</t>
         </is>
       </c>
       <c r="BC184" t="n">
-        <v>-14062467.74</v>
+        <v>-587651.08</v>
       </c>
       <c r="BD184" t="inlineStr">
         <is>
@@ -79584,32 +79584,32 @@
       </c>
       <c r="BE184" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="BH184" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK184" t="inlineStr">
@@ -79619,27 +79619,27 @@
       </c>
       <c r="BL184" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM184" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN184" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO184" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP184" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ184" t="inlineStr">
@@ -79649,17 +79649,17 @@
       </c>
       <c r="BR184" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS184" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT184" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU184" t="inlineStr">
@@ -79669,67 +79669,67 @@
       </c>
       <c r="BV184" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW184" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX184" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY184" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ184" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA184" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB184" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC184" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD184" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE184" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF184" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG184" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH184" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI184" t="inlineStr">
@@ -79746,17 +79746,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>923.167</t>
+          <t>43.587</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -79766,7 +79766,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -79776,17 +79776,17 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>-46.95</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -79796,37 +79796,37 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -79836,12 +79836,12 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -79851,27 +79851,27 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-12.11</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
@@ -79882,131 +79882,131 @@
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>-2.16</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
           <t>-2.82</t>
         </is>
       </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>-95.59</t>
+          <t>-30.74</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>-108.04</t>
+          <t>-103.68</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>17045792.0</t>
+          <t>1093260.0</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>27477728.4</t>
+          <t>1446094.4</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>51799743.1</t>
+          <t>3230021.8</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>143113653.2</t>
+          <t>3070437.26</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>-24322014</t>
+          <t>-1783927</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>-14485695.024701</t>
+          <t>-7950.011697287511</t>
         </is>
       </c>
       <c r="BC185" t="n">
-        <v>-14985931.08</v>
+        <v>-527566.91</v>
       </c>
       <c r="BD185" t="inlineStr">
         <is>
@@ -80015,32 +80015,32 @@
       </c>
       <c r="BE185" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="BH185" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK185" t="inlineStr">
@@ -80050,27 +80050,27 @@
       </c>
       <c r="BL185" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM185" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN185" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO185" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP185" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ185" t="inlineStr">
@@ -80080,17 +80080,17 @@
       </c>
       <c r="BR185" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS185" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT185" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU185" t="inlineStr">
@@ -80100,67 +80100,67 @@
       </c>
       <c r="BV185" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW185" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX185" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY185" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ185" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA185" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB185" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC185" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CD185" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE185" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF185" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG185" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH185" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI185" t="inlineStr">
@@ -80177,17 +80177,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1147.516</t>
+          <t>78.783</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -80197,7 +80197,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -80207,17 +80207,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>-44.53</t>
+          <t>-72.69</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -80227,37 +80227,37 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -80267,12 +80267,12 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
@@ -80282,27 +80282,27 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-12.11</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
@@ -80313,131 +80313,131 @@
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG186" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>-132.53</t>
+          <t>-22.95</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>-106.12</t>
+          <t>-103.39</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>21308827.0</t>
+          <t>1972853.0</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>29898216.8</t>
+          <t>1489130.8</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>53899702.9</t>
+          <t>5451729.9</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>144155769.36</t>
+          <t>3080358.98</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>-24001486</t>
+          <t>-3962599</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>-14394743.01479251</t>
+          <t>86525.78789534465</t>
         </is>
       </c>
       <c r="BC186" t="n">
-        <v>-14714838.24</v>
+        <v>-455345.78</v>
       </c>
       <c r="BD186" t="inlineStr">
         <is>
@@ -80446,32 +80446,32 @@
       </c>
       <c r="BE186" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="BH186" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK186" t="inlineStr">
@@ -80481,47 +80481,47 @@
       </c>
       <c r="BL186" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM186" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN186" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO186" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP186" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ186" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR186" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS186" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT186" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU186" t="inlineStr">
@@ -80531,67 +80531,67 @@
       </c>
       <c r="BV186" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW186" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX186" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY186" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ186" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA186" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB186" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC186" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CD186" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE186" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF186" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG186" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH186" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI186" t="inlineStr">
@@ -80608,17 +80608,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1701.929</t>
+          <t>50.542</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -80628,7 +80628,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -80638,17 +80638,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>-27.42</t>
+          <t>-73.58</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -80658,37 +80658,37 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -80698,12 +80698,12 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
@@ -80713,27 +80713,27 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-11.40</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
@@ -80744,131 +80744,131 @@
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>27.06</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>-251.30</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>-104.09</t>
+          <t>-103.20</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>30972223.0</t>
+          <t>1281899.0</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>40459215.8</t>
+          <t>1415026.2</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>55742615.0</t>
+          <t>5355571.3</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>144938850.9</t>
+          <t>3067709.32</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>-15283399</t>
+          <t>-3940545</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>-14336543.8830028</t>
+          <t>185047.8904382541</t>
         </is>
       </c>
       <c r="BC187" t="n">
-        <v>-14258786.57</v>
+        <v>-430152.49</v>
       </c>
       <c r="BD187" t="inlineStr">
         <is>
@@ -80877,32 +80877,32 @@
       </c>
       <c r="BE187" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG187" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="BH187" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK187" t="inlineStr">
@@ -80912,47 +80912,47 @@
       </c>
       <c r="BL187" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM187" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN187" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO187" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP187" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ187" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR187" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BS187" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT187" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU187" t="inlineStr">
@@ -80962,67 +80962,67 @@
       </c>
       <c r="BV187" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW187" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX187" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY187" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ187" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA187" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB187" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC187" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CD187" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE187" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF187" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CG187" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH187" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI187" t="inlineStr">
@@ -81039,17 +81039,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2106.856</t>
+          <t>71.921</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -81059,7 +81059,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -81069,17 +81069,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-67.24</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -81089,37 +81089,37 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2024-07-16 00:00:00</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
@@ -81129,12 +81129,12 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
@@ -81144,27 +81144,27 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-10.53</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-42.50</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
@@ -81175,131 +81175,131 @@
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
           <t>19.31</t>
         </is>
       </c>
-      <c r="AN188" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>18.26</t>
-        </is>
-      </c>
-      <c r="AP188" t="inlineStr">
-        <is>
-          <t>-644.99</t>
-        </is>
-      </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>-101.52</t>
+          <t>-103.17</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>165783455.3193642</t>
+          <t>81052983.11271676</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>39107734.0</t>
+          <t>1838632.0</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>43583661.6</t>
+          <t>1764250.2</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>66456027.4</t>
+          <t>5384662.9</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>146247235.0</t>
+          <t>3070701.62</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>-22872365</t>
+          <t>-3620412</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>-14350681.57674556</t>
+          <t>296902.5044127645</t>
         </is>
       </c>
       <c r="BC188" t="n">
-        <v>-14133405.66</v>
+        <v>-304768.7</v>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
@@ -81308,32 +81308,32 @@
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025/08/08</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="BH188" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BK188" t="inlineStr">
@@ -81343,27 +81343,27 @@
       </c>
       <c r="BL188" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BM188" t="inlineStr">
         <is>
-          <t>-6.269044207432034</t>
+          <t>-62.65714600794001</t>
         </is>
       </c>
       <c r="BN188" t="inlineStr">
         <is>
-          <t>-8.980265976923736</t>
+          <t>-82.43555163649567</t>
         </is>
       </c>
       <c r="BO188" t="inlineStr">
         <is>
-          <t>-6.798643782162525</t>
+          <t>-38.05762955491554</t>
         </is>
       </c>
       <c r="BP188" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ188" t="inlineStr">
@@ -81373,17 +81373,17 @@
       </c>
       <c r="BR188" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BS188" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT188" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU188" t="inlineStr">
@@ -81393,67 +81393,67 @@
       </c>
       <c r="BV188" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="BW188" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-57.24%</t>
         </is>
       </c>
       <c r="BX188" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="BY188" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="BZ188" t="inlineStr">
         <is>
-          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+          <t>生技產品61.00%、化學合成產品37.00%、其他2.00% (2024年)</t>
         </is>
       </c>
       <c r="CA188" t="inlineStr">
         <is>
-          <t>永光-化學工業-上市</t>
+          <t>中化生-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CB188" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CC188" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CD188" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE188" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF188" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CG188" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="CH188" t="inlineStr">
         <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+          <t>** 製藥 - 中藥材、西藥原料藥</t>
         </is>
       </c>
       <c r="CI188" t="inlineStr">
@@ -81475,34 +81475,34 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>-3.65</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3690.931</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>1544.127</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
       <c r="I189" t="inlineStr">
         <is>
           <t>-2.49</t>
@@ -81510,7 +81510,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -81575,7 +81575,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
@@ -81585,17 +81585,17 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
@@ -81616,278 +81616,4588 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>70.47</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>18.92</t>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>11.60</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>-110.12</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>69701539.0</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>66070275.6</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>46567948.0</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>139781443.8</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>19502327</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>-9002419.174373947</t>
+        </is>
+      </c>
+      <c r="BC189" t="n">
+        <v>595819.37</v>
+      </c>
+      <c r="BD189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="BH189" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI189" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ189" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM189" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN189" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO189" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP189" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BQ189" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR189" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BS189" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT189" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV189" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW189" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX189" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY189" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ189" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA189" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB189" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC189" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="CD189" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE189" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="CF189" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CG189" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH189" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI189" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>6098.179</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>35.34</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>9.02</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>94.74</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>98.25</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>19.28</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>18.56</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>-110.41</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>118098812.0</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>57508673.0</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>42493200.7</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>139366944.98</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>15015472</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>-10747553.45557433</t>
+        </is>
+      </c>
+      <c r="BC190" t="n">
+        <v>-248487.7</v>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>15.32</t>
+        </is>
+      </c>
+      <c r="BH190" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI190" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ190" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM190" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN190" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO190" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP190" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ190" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR190" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BS190" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT190" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV190" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW190" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX190" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY190" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ190" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA190" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB190" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC190" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="CD190" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="CE190" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CF190" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="CG190" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH190" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI190" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>3990.59</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>11.01</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>84.85</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>18.94</t>
+        </is>
+      </c>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>19.26</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>18.52</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>11.69</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>-111.24</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>76501817.0</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>37298069.0</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>33598142.9</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>138751251.62</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>3699926</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>-12656474.50287244</t>
+        </is>
+      </c>
+      <c r="BC191" t="n">
+        <v>-6631188.2</v>
+      </c>
+      <c r="BD191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE191" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG191" t="inlineStr">
+        <is>
+          <t>15.62</t>
+        </is>
+      </c>
+      <c r="BH191" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI191" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ191" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM191" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN191" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO191" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP191" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ191" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR191" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BS191" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT191" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV191" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW191" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX191" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY191" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ191" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA191" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB191" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC191" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CD191" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="CE191" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CF191" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="CG191" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH191" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI191" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2201.558</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-2.43</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-21.28</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>58.92</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>18.94</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>18.48</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>-19.00</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr">
+        <is>
+          <t>-111.57</t>
+        </is>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>41778653.0</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>26259471.0</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>33359343.4</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>138380212.08</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>-7099872</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>-13751981.10415282</t>
+        </is>
+      </c>
+      <c r="BC192" t="n">
+        <v>-11055682.73</v>
+      </c>
+      <c r="BD192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE192" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF192" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG192" t="inlineStr">
+        <is>
+          <t>13.81</t>
+        </is>
+      </c>
+      <c r="BH192" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI192" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ192" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK192" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL192" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM192" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN192" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO192" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP192" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ192" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR192" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="BS192" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT192" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV192" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW192" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX192" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY192" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ192" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA192" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB192" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC192" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="CD192" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="CE192" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="CF192" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CG192" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH192" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI192" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1303.305</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-28.79</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>-6.53</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>54.55</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>18.53</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>18.94</t>
+        </is>
+      </c>
+      <c r="AN193" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>-47.05</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT193" t="inlineStr">
+        <is>
+          <t>-111.02</t>
+        </is>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>24270557.0</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>24098185.0</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>33840923.3</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>140302562.8</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>-9742738</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>-14242217.17306861</t>
+        </is>
+      </c>
+      <c r="BC193" t="n">
+        <v>-13261204.38</v>
+      </c>
+      <c r="BD193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE193" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF193" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG193" t="inlineStr">
+        <is>
+          <t>11.71</t>
+        </is>
+      </c>
+      <c r="BH193" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI193" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ193" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL193" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM193" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN193" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO193" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP193" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ193" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR193" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BS193" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT193" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV193" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW193" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX193" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY193" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ193" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA193" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB193" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC193" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CD193" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="CE193" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="CF193" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="CG193" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH193" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI193" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>1467.935</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG189" t="inlineStr">
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-35.74</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>-7.04</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>22.22</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>22.88</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>-2.73</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>18.47</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AN194" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>18.42</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>-69.03</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr">
+        <is>
+          <t>-109.72</t>
+        </is>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>26893526.0</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>27065620.4</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>42116606.3</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>141853229.66</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>-15050985</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>-14420583.13473333</t>
+        </is>
+      </c>
+      <c r="BC194" t="n">
+        <v>-14062467.74</v>
+      </c>
+      <c r="BD194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE194" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF194" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="BH194" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI194" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ194" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK194" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL194" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM194" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN194" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO194" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP194" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ194" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR194" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BS194" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT194" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV194" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW194" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX194" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY194" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ194" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA194" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB194" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC194" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="CD194" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CE194" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="CF194" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CG194" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH194" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI194" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>923.167</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-46.95</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>-7.29</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>18.52</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="AN195" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>-95.59</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT195" t="inlineStr">
+        <is>
+          <t>-108.04</t>
+        </is>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>17045792.0</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>27477728.4</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>51799743.1</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>143113653.2</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>-24322014</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>-14485695.024701</t>
+        </is>
+      </c>
+      <c r="BC195" t="n">
+        <v>-14985931.08</v>
+      </c>
+      <c r="BD195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE195" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF195" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG195" t="inlineStr">
+        <is>
+          <t>10.81</t>
+        </is>
+      </c>
+      <c r="BH195" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI195" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ195" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK195" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL195" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM195" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN195" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO195" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP195" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ195" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR195" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BS195" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT195" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV195" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW195" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX195" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY195" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ195" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA195" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB195" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC195" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="CD195" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CE195" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="CF195" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="CG195" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH195" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI195" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1147.516</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-44.53</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>-5.78</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>32.14</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="AN196" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>18.34</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>-132.53</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr">
+        <is>
+          <t>-106.12</t>
+        </is>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>21308827.0</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>29898216.8</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>53899702.9</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>144155769.36</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>-24001486</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>-14394743.01479251</t>
+        </is>
+      </c>
+      <c r="BC196" t="n">
+        <v>-14714838.24</v>
+      </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG196" t="inlineStr">
+        <is>
+          <t>12.61</t>
+        </is>
+      </c>
+      <c r="BH196" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI196" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ196" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK196" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL196" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM196" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN196" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO196" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP196" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ196" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR196" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="BS196" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT196" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV196" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW196" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX196" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY196" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ196" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA196" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB196" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC196" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CD196" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="CE196" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="CF196" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="CG196" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH196" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI196" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1701.929</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-27.42</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>-7.79</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>19.22</t>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t>19.21</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>-251.30</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>-104.09</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>30972223.0</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>40459215.8</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>55742615.0</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>144938850.9</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>-15283399</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>-14336543.8830028</t>
+        </is>
+      </c>
+      <c r="BC197" t="n">
+        <v>-14258786.57</v>
+      </c>
+      <c r="BD197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE197" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF197" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG197" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="BH197" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI197" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ197" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK197" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL197" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM197" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN197" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO197" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP197" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ197" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR197" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BS197" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT197" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV197" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW197" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX197" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY197" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ197" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA197" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB197" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC197" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CD197" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="CE197" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="CF197" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="CG197" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH197" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI197" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>-2.39</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2106.856</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-34.42</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>-8.04</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH189" t="inlineStr">
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>-2.50</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>-2.80</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>18.77</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>19.31</t>
+        </is>
+      </c>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>18.26</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>-644.99</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>-101.52</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>165783455.3193642</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>39107734.0</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>43583661.6</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>66456027.4</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>146247235.0</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>-22872365</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>-14350681.57674556</t>
+        </is>
+      </c>
+      <c r="BC198" t="n">
+        <v>-14133405.66</v>
+      </c>
+      <c r="BD198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE198" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="BF198" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG198" t="inlineStr">
+        <is>
+          <t>9.91</t>
+        </is>
+      </c>
+      <c r="BH198" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BI198" t="inlineStr">
+        <is>
+          <t>永光</t>
+        </is>
+      </c>
+      <c r="BJ198" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BK198" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL198" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BM198" t="inlineStr">
+        <is>
+          <t>-6.269044207432034</t>
+        </is>
+      </c>
+      <c r="BN198" t="inlineStr">
+        <is>
+          <t>-8.980265976923736</t>
+        </is>
+      </c>
+      <c r="BO198" t="inlineStr">
+        <is>
+          <t>-6.798643782162525</t>
+        </is>
+      </c>
+      <c r="BP198" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ198" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR198" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BS198" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BT198" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BU198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV198" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="BW198" t="inlineStr">
+        <is>
+          <t>-5.61%</t>
+        </is>
+      </c>
+      <c r="BX198" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="BY198" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="BZ198" t="inlineStr">
+        <is>
+          <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA198" t="inlineStr">
+        <is>
+          <t>永光-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CB198" t="inlineStr">
+        <is>
+          <t>化學工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC198" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="CD198" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CE198" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF198" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CG198" t="inlineStr">
+        <is>
+          <t>14.88</t>
+        </is>
+      </c>
+      <c r="CH198" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CI198" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1544.127</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-14.90</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>-5.78</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
         <is>
           <t>-1.21</t>
         </is>
       </c>
-      <c r="AI189" t="inlineStr">
+      <c r="AI199" t="inlineStr">
         <is>
           <t>-2.35</t>
         </is>
       </c>
-      <c r="AJ189" t="inlineStr">
+      <c r="AJ199" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="AK189" t="inlineStr">
+      <c r="AK199" t="inlineStr">
         <is>
           <t>5.33</t>
         </is>
       </c>
-      <c r="AL189" t="inlineStr">
+      <c r="AL199" t="inlineStr">
         <is>
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM189" t="inlineStr">
+      <c r="AM199" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="AN189" t="inlineStr">
+      <c r="AN199" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
       </c>
-      <c r="AO189" t="inlineStr">
+      <c r="AO199" t="inlineStr">
         <is>
           <t>18.23</t>
         </is>
       </c>
-      <c r="AP189" t="inlineStr">
+      <c r="AP199" t="inlineStr">
         <is>
           <t>-841.37</t>
         </is>
       </c>
-      <c r="AQ189" t="inlineStr">
+      <c r="AQ199" t="inlineStr">
         <is>
           <t>-0.09</t>
         </is>
       </c>
-      <c r="AR189" t="inlineStr">
+      <c r="AR199" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AS189" t="inlineStr">
+      <c r="AS199" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="AT189" t="inlineStr">
+      <c r="AT199" t="inlineStr">
         <is>
           <t>-99.07</t>
         </is>
       </c>
-      <c r="AU189" t="inlineStr">
+      <c r="AU199" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AV189" t="inlineStr">
+      <c r="AV199" t="inlineStr">
         <is>
           <t>165783455.3193642</t>
         </is>
       </c>
-      <c r="AW189" t="inlineStr">
+      <c r="AW199" t="inlineStr">
         <is>
           <t>28954066.0</t>
         </is>
       </c>
-      <c r="AX189" t="inlineStr">
+      <c r="AX199" t="inlineStr">
         <is>
           <t>57167592.2</t>
         </is>
       </c>
-      <c r="AY189" t="inlineStr">
+      <c r="AY199" t="inlineStr">
         <is>
           <t>67175431.3</t>
         </is>
       </c>
-      <c r="AZ189" t="inlineStr">
+      <c r="AZ199" t="inlineStr">
         <is>
           <t>150452772.08</t>
         </is>
       </c>
-      <c r="BA189" t="inlineStr">
+      <c r="BA199" t="inlineStr">
         <is>
           <t>-10007839</t>
         </is>
       </c>
-      <c r="BB189" t="inlineStr">
+      <c r="BB199" t="inlineStr">
         <is>
           <t>-14390186.28919575</t>
         </is>
       </c>
-      <c r="BC189" t="n">
+      <c r="BC199" t="n">
         <v>-14321187.48</v>
       </c>
-      <c r="BD189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE189" t="inlineStr">
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
         <is>
           <t>16.65</t>
         </is>
       </c>
-      <c r="BF189" t="inlineStr">
+      <c r="BF199" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
       </c>
-      <c r="BG189" t="inlineStr">
+      <c r="BG199" t="inlineStr">
         <is>
           <t>12.61</t>
         </is>
       </c>
-      <c r="BH189" t="inlineStr">
+      <c r="BH199" t="inlineStr">
         <is>
           <t>永光</t>
         </is>
       </c>
-      <c r="BI189" t="inlineStr">
+      <c r="BI199" t="inlineStr">
         <is>
           <t>永光</t>
         </is>
       </c>
-      <c r="BJ189" t="inlineStr">
+      <c r="BJ199" t="inlineStr">
         <is>
           <t>化學工業</t>
         </is>
       </c>
-      <c r="BK189" t="inlineStr">
+      <c r="BK199" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL189" t="inlineStr">
+      <c r="BL199" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="BM189" t="inlineStr">
+      <c r="BM199" t="inlineStr">
         <is>
           <t>-6.269044207432034</t>
         </is>
       </c>
-      <c r="BN189" t="inlineStr">
+      <c r="BN199" t="inlineStr">
         <is>
           <t>-8.980265976923736</t>
         </is>
       </c>
-      <c r="BO189" t="inlineStr">
+      <c r="BO199" t="inlineStr">
         <is>
           <t>-6.798643782162525</t>
         </is>
       </c>
-      <c r="BP189" t="inlineStr">
+      <c r="BP199" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ189" t="inlineStr">
+      <c r="BQ199" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR189" t="inlineStr">
+      <c r="BR199" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="BS189" t="inlineStr">
+      <c r="BS199" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="BT189" t="inlineStr">
+      <c r="BT199" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="BU189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV189" t="inlineStr">
+      <c r="BU199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV199" t="inlineStr">
         <is>
           <t>15.95%</t>
         </is>
       </c>
-      <c r="BW189" t="inlineStr">
+      <c r="BW199" t="inlineStr">
         <is>
           <t>-5.61%</t>
         </is>
       </c>
-      <c r="BX189" t="inlineStr">
+      <c r="BX199" t="inlineStr">
         <is>
           <t>48.32</t>
         </is>
       </c>
-      <c r="BY189" t="inlineStr">
+      <c r="BY199" t="inlineStr">
         <is>
           <t>10133</t>
         </is>
       </c>
-      <c r="BZ189" t="inlineStr">
+      <c r="BZ199" t="inlineStr">
         <is>
           <t>色料化學品50.76%、特用化學品25.72%、其他電子化學品14.33%、光阻劑6.43%、前列腺素2.36%、醫藥化學品-其他原料藥0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA189" t="inlineStr">
+      <c r="CA199" t="inlineStr">
         <is>
           <t>永光-化學工業-上市</t>
         </is>
       </c>
-      <c r="CB189" t="inlineStr">
+      <c r="CB199" t="inlineStr">
         <is>
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="CC189" t="inlineStr">
+      <c r="CC199" t="inlineStr">
         <is>
           <t>18.85</t>
         </is>
       </c>
-      <c r="CD189" t="inlineStr">
+      <c r="CD199" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CE189" t="inlineStr">
+      <c r="CE199" t="inlineStr">
         <is>
           <t>18.65</t>
         </is>
       </c>
-      <c r="CF189" t="inlineStr">
+      <c r="CF199" t="inlineStr">
         <is>
           <t>18.75</t>
         </is>
       </c>
-      <c r="CG189" t="inlineStr">
+      <c r="CG199" t="inlineStr">
         <is>
           <t>14.88</t>
         </is>
       </c>
-      <c r="CH189" t="inlineStr">
+      <c r="CH199" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 其他電腦及週邊設備之零組件** 平面顯示器 - 化學品(如光阻劑、靶材等)** 石化及塑橡膠 - 顏染料、接著劑(合成樹脂)、橡塑膠添加劑** 製藥 - 中藥材、西藥原料藥** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI189" t="inlineStr">
+      <c r="CI199" t="inlineStr">
         <is>
           <t>False</t>
         </is>
